--- a/excel/23127183_HW06_TestCases.xlsx
+++ b/excel/23127183_HW06_TestCases.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" style="1" min="1" max="1"/>
@@ -464,7 +464,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>&gt; Sinh luc: 2026-08-31T05:58:33.949Z</t>
+          <t>&gt; Sinh luc: 2026-09-02T15:27:57.633Z</t>
         </is>
       </c>
     </row>
@@ -488,28 +488,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>| api-01-login | 53 | 53 | 44 | 9 | 23127183_api-01-login_20260831-124339.json |</t>
+          <t>| api-01-login | 53 | 53 | 44 | 9 | 23127183_api-01-login_20260902-222409.json |</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | 59 | 59 | 44 | 15 | 23127183_api-02-apply-coupon_20260831-125109.json |</t>
+          <t>| api-02-apply-coupon | 59 | 59 | 46 | 13 | 23127183_api-02-apply-coupon_20260902-222617.json |</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>| api-03-product-update | 51 | 51 | 26 | 25 | 23127183_api-03-product-update_20260831-125812.json |</t>
+          <t>| api-03-product-update | 51 | 51 | 26 | 25 | 23127183_api-03-product-update_20260902-222733.json |</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>| Tong | 163 | 163 | 114 | 49 | |</t>
+          <t>| Tong | 163 | 163 | 116 | 47 | |</t>
         </is>
       </c>
     </row>
@@ -543,365 +543,351 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-016 undefined | TC-LOGIN-016: sai content-type - khong duoc crash 500 |</t>
+          <t>| api-01-login | TC-LOGIN-016 | TC-LOGIN-016: sai content-type - khong duoc crash 500 |</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-103 undefined | TC-LOGIN-103 SV: tai khoan dang ky sau phai dang nhap duoc |</t>
+          <t>| api-01-login | TC-LOGIN-103 | TC-LOGIN-103 SV: tai khoan dang ky sau phai dang nhap duoc |</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-022 undefined | TC-LOGIN-022: dung mat khau o request thu 3 - AI du doan THANH CONG |</t>
+          <t>| api-01-login | TC-LOGIN-022 | TC-LOGIN-022: dung mat khau o request thu 3 - AI du doan THANH CONG |</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-028 undefined | TC-LOGIN-028 SEC-01: khong lo password trong response |</t>
+          <t>| api-01-login | TC-LOGIN-028 | TC-LOGIN-028 SEC-01: khong lo password trong response |</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-029 undefined | TC-LOGIN-029 SEC-01: khong lo cot noi bo |</t>
+          <t>| api-01-login | TC-LOGIN-029 | TC-LOGIN-029 SEC-01: khong lo cot noi bo |</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-030 undefined | TC-LOGIN-030 SEC-02: JWT phai co exp |</t>
+          <t>| api-01-login | TC-LOGIN-030 | TC-LOGIN-030 SEC-02: JWT phai co exp |</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-036 undefined | TC-LOGIN-036: body khong phai JSON - khong duoc la HTML loi |</t>
+          <t>| api-01-login | TC-LOGIN-036 | TC-LOGIN-036: body khong phai JSON - khong duoc la HTML loi |</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-037 undefined | TC-LOGIN-037: khong lo field thua |</t>
+          <t>| api-01-login | TC-LOGIN-037 | TC-LOGIN-037: khong lo field thua |</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| api-01-login | TC-LOGIN-104 undefined | TC-LOGIN-104 SV: khong lo duong dan he thong khi loi parse JSON |</t>
+          <t>| api-01-login | TC-LOGIN-104 | TC-LOGIN-104 SV: khong lo duong dan he thong khi loi parse JSON |</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-001 undefined | TC-COUPON-001: SAVE10 dung cong thuc FR-09 |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-001 | TC-COUPON-001: SAVE10 dung cong thuc FR-09 |</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-023 undefined | TC-COUPON-023: huy don dang shipping bi chan |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-023 | TC-COUPON-023: huy don dang shipping bi chan |</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-028 undefined | TC-COUPON-028: canceled la trang thai ket thuc |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-028 | TC-COUPON-028: canceled la trang thai ket thuc |</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-102 undefined | TC-COUPON-102 buoc 1: VIP100 lan 1 hop le |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-031 | TC-COUPON-031 SEC-02: khong token phai bi chan |</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-102c undefined | TC-COUPON-102c: VIP100 lan 2 hop le |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-032 | TC-COUPON-032 SEC-03: user thuong khong duoc doi trang thai don |</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-031 undefined | TC-COUPON-031 SEC-02: khong token phai bi chan |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-033 | TC-COUPON-033 IDOR: xem don khong token phai bi chan |</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-032 undefined | TC-COUPON-032 SEC-03: user thuong khong duoc doi trang thai don |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-034 | TC-COUPON-034: khong duoc tin total_amount tu client |</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-033 undefined | TC-COUPON-033 IDOR: xem don khong token phai bi chan |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-036 | TC-COUPON-036 IDOR: user_id tu body la loi thiet ke |</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-034 undefined | TC-COUPON-034: khong duoc tin total_amount tu client |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-037 | TC-COUPON-037: khong gui user_id khong duoc bo qua C5 |</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-036 undefined | TC-COUPON-036 IDOR: user_id tu body la loi thiet ke |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-039 | TC-COUPON-039 SEC-03: user thuong khong duoc goi endpoint admin (target thu 2) |</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-037 undefined | TC-COUPON-037: khong gui user_id khong duoc bo qua C5 |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-101 | TC-COUPON-101 SV: checkout gia mao gia phai bi chan |</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-039 undefined | TC-COUPON-039 SEC-03: user thuong khong duoc goi endpoint admin (target thu 2) |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-042 | TC-COUPON-042: discount_amount khong am |</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-101 undefined | TC-COUPON-101 SV: checkout gia mao gia phai bi chan |</t>
+          <t>| api-02-apply-coupon | TC-COUPON-043 | TC-COUPON-043: final_amount khong duoc lon hon total_amount |</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-042 undefined | TC-COUPON-042: discount_amount khong am |</t>
+          <t>| api-03-product-update | TC-PRODUPD-002 | TC-PRODUPD-002: name rong phai bi tu choi |</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | TC-COUPON-043 undefined | TC-COUPON-043: final_amount khong duoc lon hon total_amount |</t>
+          <t>| api-03-product-update | TC-PRODUPD-004 | TC-PRODUPD-004: name 256 ky tu phai bi tu choi |</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-002 undefined | TC-PRODUPD-002: name rong phai bi tu choi |</t>
+          <t>| api-03-product-update | TC-PRODUPD-006 | TC-PRODUPD-006: price = 0 phai bi tu choi |</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-004 undefined | TC-PRODUPD-004: name 256 ky tu phai bi tu choi |</t>
+          <t>| api-03-product-update | TC-PRODUPD-007 | TC-PRODUPD-007: price am phai bi tu choi |</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-006 undefined | TC-PRODUPD-006: price = 0 phai bi tu choi |</t>
+          <t>| api-03-product-update | TC-PRODUPD-008 | TC-PRODUPD-008: price sai kieu bi tu choi |</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-007 undefined | TC-PRODUPD-007: price am phai bi tu choi |</t>
+          <t>| api-03-product-update | TC-PRODUPD-009 | TC-PRODUPD-009: category_id khong ton tai bi tu choi |</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-008 undefined | TC-PRODUPD-008: price sai kieu bi tu choi |</t>
+          <t>| api-03-product-update | TC-PRODUPD-010 | TC-PRODUPD-010: thieu category_id bi tu choi |</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-009 undefined | TC-PRODUPD-009: category_id khong ton tai bi tu choi |</t>
+          <t>| api-03-product-update | TC-PRODUPD-014 | TC-PRODUPD-014: id khong ton tai phai 404 |</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-010 undefined | TC-PRODUPD-010: thieu category_id bi tu choi |</t>
+          <t>| api-03-product-update | TC-PRODUPD-015 | TC-PRODUPD-015: id sai kieu phai 400 |</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-014 undefined | TC-PRODUPD-014: id khong ton tai phai 404 |</t>
+          <t>| api-03-product-update | TC-PRODUPD-022 | TC-PRODUPD-022: cac truong khac KHONG duoc mat sau PUT mot phan |</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-015 undefined | TC-PRODUPD-015: id sai kieu phai 400 |</t>
+          <t>| api-03-product-update | TC-PRODUPD-024 | TC-PRODUPD-024: sau xoa GET phai 404 |</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-022 undefined | TC-PRODUPD-022: cac truong khac KHONG duoc mat sau PUT mot phan |</t>
+          <t>| api-03-product-update | TC-PRODUPD-025 | TC-PRODUPD-025: PUT len san pham da xoa phai 404 |</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-024 undefined | TC-PRODUPD-024: sau xoa GET phai 404 |</t>
+          <t>| api-03-product-update | TC-PRODUPD-105 | TC-PRODUPD-105 SV: body rong phai bi tu choi, khong duoc xoa sach du lieu |</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-025 undefined | TC-PRODUPD-025: PUT len san pham da xoa phai 404 |</t>
+          <t>| api-03-product-update | TC-PRODUPD-027 | TC-PRODUPD-027 SEC-02: PUT khong token phai bi chan |</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-105 undefined | TC-PRODUPD-105 SV: body rong phai bi tu choi, khong duoc xoa sach du lieu |</t>
+          <t>| api-03-product-update | TC-PRODUPD-028 | TC-PRODUPD-028: du lieu KHONG duoc doi neu SEC-02 dung |</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-027 undefined | TC-PRODUPD-027 SEC-02: PUT khong token phai bi chan |</t>
+          <t>| api-03-product-update | TC-PRODUPD-029 | TC-PRODUPD-029 SEC-03: user thuong khong duoc sua |</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-028 undefined | TC-PRODUPD-028: du lieu KHONG duoc doi neu SEC-02 dung |</t>
+          <t>| api-03-product-update | TC-PRODUPD-030 | TC-PRODUPD-030: token rac phai bi chan |</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-029 undefined | TC-PRODUPD-029 SEC-03: user thuong khong duoc sua |</t>
+          <t>| api-03-product-update | TC-PRODUPD-031 | TC-PRODUPD-031 SEC-05: SQLi trong id bi tu choi dung dinh dang |</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-030 undefined | TC-PRODUPD-030: token rac phai bi chan |</t>
+          <t>| api-03-product-update | TC-PRODUPD-102 | TC-PRODUPD-102 SV: DELETE khong token phai bi chan |</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-031 undefined | TC-PRODUPD-031 SEC-05: SQLi trong id bi tu choi dung dinh dang |</t>
+          <t>| api-03-product-update | TC-PRODUPD-038 | TC-PRODUPD-038: id le - price la number |</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-102 undefined | TC-PRODUPD-102 SV: DELETE khong token phai bi chan |</t>
+          <t>| api-03-product-update | TC-PRODUPD-039 | TC-PRODUPD-039: id chan - price VAN PHAI la number |</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-038 undefined | TC-PRODUPD-038: id le - price la number |</t>
+          <t>| api-03-product-update | TC-PRODUPD-040 | TC-PRODUPD-040: schema loi 400 |</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-039 undefined | TC-PRODUPD-039: id chan - price VAN PHAI la number |</t>
+          <t>| api-03-product-update | TC-PRODUPD-042 | TC-PRODUPD-042: id khong ton tai phai 404 khong phai 200 rong |</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-040 undefined | TC-PRODUPD-040: schema loi 400 |</t>
+          <t>| api-03-product-update | TC-PRODUPD-043 | TC-PRODUPD-043: PUT id khong ton tai tra loi dung, khong bao thanh cong gia |</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-042 undefined | TC-PRODUPD-042: id khong ton tai phai 404 khong phai 200 rong |</t>
+          <t>| api-03-product-update | TC-PRODUPD-045 | TC-PRODUPD-045: body loi khong duoc la HTML co stack trace |</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>| api-03-product-update | TC-PRODUPD-043 undefined | TC-PRODUPD-043: PUT id khong ton tai tra loi dung, khong bao thanh cong gia |</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>| api-03-product-update | TC-PRODUPD-045 undefined | TC-PRODUPD-045: body loi khong duoc la HTML co stack trace |</t>
+          <t>&gt; Assertion do o day la KET QUA MONG DOI. Expected cua bo test bam theo DAC TA (FR/SEC),</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>&gt; khong bam theo hanh vi hien tai cua SUT. SUT co bug co y -&gt; do = phat hien duoc bug.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
-        <is>
-          <t>&gt; Assertion do o day la KET QUA MONG DOI. Expected cua bo test bam theo DAC TA (FR/SEC),</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>&gt; khong bam theo hanh vi hien tai cua SUT. SUT co bug co y -&gt; do = phat hien duoc bug.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
         <is>
           <t>&gt; Sua expected cho khop SUT la cach nhanh nhat de bo test mat het gia tri.</t>
         </is>
@@ -9723,7 +9709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A574"/>
+  <dimension ref="A1:A576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" style="1" min="1" max="1"/>
@@ -9749,405 +9735,409 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>- GitHub Issues: https://github.com/DuyPham111/HW06/issues _(chưa tạo — xem [docs/CAN-LAM-TIEP-THEO.md](../docs/CAN-LAM-TIEP-THEO.md))_</t>
+          <t>- GitHub Issues: https://github.com/DuyPham111/HW06/issues — 27/27 đã tạo (#1–#27), mỗi issue</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>- Script tái hiện: bash bug-report/verify-bugs.sh → output ở verify-bugs-output.txt</t>
+          <t>gắn label mức độ + API. Còn thiếu ảnh minh hoạ (kéo-thả thủ công, xem docs/CAN-LAM-TIEP-THEO.md)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>- Số liệu request/assertion lấy từ [test-cases/test-summary/summary.md](../test-cases/test-summary/summary.md)</t>
+          <t>- Script tái hiện: bash bug-report/verify-bugs.sh → output ở verify-bugs-output.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>- Số liệu request/assertion lấy từ [test-cases/test-summary/summary.md](../test-cases/test-summary/summary.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>(sinh tự động bằng npm run summary, không gõ tay).</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>&gt; Luật: mọi bug dưới đây đã tái hiện bằng request thật (curl hoặc Newman), không phải suy từ</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>&gt; Luật: mọi bug dưới đây đã tái hiện bằng request thật (curl hoặc Newman), không phải suy từ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>&gt; đọc code. Giả thuyết chưa kiểm chứng nằm ở §4.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>## 1. Tổng hợp</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>| Mức | Số bug |</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>|---|--:|</t>
+          <t>| Mức | Số bug |</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>| Critical | 13 |</t>
+          <t>|---|--:|</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>| High | 9 |</t>
+          <t>| Critical | 13 |</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>| Medium | 4 |</t>
+          <t>| High | 9 |</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| Low | 1 |</t>
+          <t>| Medium | 4 |</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>| Low | 1 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>| Tổng | 27 |</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>## 2. Bảng quy đổi assertion đỏ → bug</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>&gt; 163 request · 163 assertion · 49 đỏ (API-01: 9 · API-02: 15 · API-03: 25).</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>&gt; Không phải mọi bug đều lộ qua assertion đỏ — BUG-01 (DoS lockout) và BUG-19 (crash server) được</t>
+          <t>&gt; 163 request · 163 assertion · 47 đỏ (API-01: 9 · API-02: 13 · API-03: 25).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>&gt; chứng minh bằng chuỗi request mà assertion PASS (expected chính là hành vi khai thác được, và</t>
+          <t>&gt; Không phải mọi bug đều lộ qua assertion đỏ — BUG-01 (DoS lockout) và BUG-19 (crash server) được</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>&gt; chứng minh bằng chuỗi request mà assertion PASS (expected chính là hành vi khai thác được, và</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>&gt; nó khớp thật) — xem ghi chú riêng ở từng bug đó.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-    </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>| Bug | Mức | API | Test case liên quan | Assertion đỏ |</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>|---|---|---|---|--:|</t>
+          <t>| Bug | Mức | API | Test case liên quan | Assertion đỏ | Issue |</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>| BUG-01 | Critical | 01 | TC-LOGIN-031, 101, 101b | 0 *(pass = khai thác thành công)* |</t>
+          <t>|---|---|---|---|--:|---|</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>| BUG-02 | High | 01 | TC-LOGIN-022 | 1 |</t>
+          <t>| BUG-01 | Critical | 01 | TC-LOGIN-031, 101, 101b | 0 *(pass = khai thác thành công)* | [#2](https://github.com/DuyPham111/HW06/issues/2) |</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| BUG-03 | Critical | 01 | TC-LOGIN-028 | 1 |</t>
+          <t>| BUG-02 | High | 01 | TC-LOGIN-022 | 1 | [#3](https://github.com/DuyPham111/HW06/issues/3) |</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>| BUG-04 | High | 01 | TC-LOGIN-029, 037 | 2 |</t>
+          <t>| BUG-03 | Critical | 01 | TC-LOGIN-028 | 1 | [#4](https://github.com/DuyPham111/HW06/issues/4) |</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| BUG-05 | Medium | 01 | TC-LOGIN-030 | 1 |</t>
+          <t>| BUG-04 | High | 01 | TC-LOGIN-029, 037 | 2 | [#5](https://github.com/DuyPham111/HW06/issues/5) |</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>| BUG-06 | High | 01 | TC-LOGIN-016 | 1 |</t>
+          <t>| BUG-05 | Medium | 01 | TC-LOGIN-030 | 1 | [#6](https://github.com/DuyPham111/HW06/issues/6) |</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>| BUG-07 | High | 01 | TC-LOGIN-036, 104 | 2 |</t>
+          <t>| BUG-06 | High | 01 | TC-LOGIN-016 | 1 | [#7](https://github.com/DuyPham111/HW06/issues/7) |</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>| BUG-08 | Critical | 01 | TC-LOGIN-103 | 1 |</t>
+          <t>| BUG-07 | High | 01 | TC-LOGIN-036, 104 | 2 | [#8](https://github.com/DuyPham111/HW06/issues/8) |</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>| BUG-09 | Medium | 01 | TC-LOGIN-102 (đối chứng với TC-LOGIN-023c) | 0 *(cả 2 đều pass, lộ ra khi SO SÁNH)* |</t>
+          <t>| BUG-08 | Critical | 01 | TC-LOGIN-103 | 1 | [#9](https://github.com/DuyPham111/HW06/issues/9) |</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>| BUG-10 | Critical | 02 | TC-COUPON-001, 042, 043 | 3 |</t>
+          <t>| BUG-09 | Medium | 01 | TC-LOGIN-102 (đối chứng với TC-LOGIN-023c) | 0 *(cả 2 đều pass, lộ ra khi SO SÁNH)* | [#10](https://github.com/DuyPham111/HW06/issues/10) |</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>| BUG-11 | Critical | 02 | TC-COUPON-031 | 1 |</t>
+          <t>| BUG-10 | Critical | 02 | TC-COUPON-001, 042, 043 | 3 | [#11](https://github.com/DuyPham111/HW06/issues/11) |</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>| BUG-12 | High | 02 | TC-COUPON-004 | 1 |</t>
+          <t>| BUG-11 | Critical | 02 | TC-COUPON-031 | 1 | [#12](https://github.com/DuyPham111/HW06/issues/12) |</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>| BUG-13 | Critical | 02 | TC-COUPON-036, 037 | 2 |</t>
+          <t>| BUG-12 | High | 02 | TC-COUPON-004 | 1 | [#13](https://github.com/DuyPham111/HW06/issues/13) |</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>| BUG-14 | Critical | 02 | TC-COUPON-034, 101 | 2 |</t>
+          <t>| BUG-13 | Critical | 02 | TC-COUPON-036, 037 | 2 | [#14](https://github.com/DuyPham111/HW06/issues/14) |</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>| BUG-15 | High | 02 | TC-COUPON-033 | 1 |</t>
+          <t>| BUG-14 | Critical | 02 | TC-COUPON-034, 101 | 2 | [#15](https://github.com/DuyPham111/HW06/issues/15) |</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>| BUG-16 | High | 02 | TC-COUPON-023 | 1 |</t>
+          <t>| BUG-15 | High | 02 | TC-COUPON-033 | 1 | [#16](https://github.com/DuyPham111/HW06/issues/16) |</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>| BUG-17 | High | 02 | TC-COUPON-028 | 1 |</t>
+          <t>| BUG-16 | High | 02 | TC-COUPON-023 | 1 | [#17](https://github.com/DuyPham111/HW06/issues/17) |</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>| BUG-18 | Critical | 02 | TC-COUPON-032, 039 | 2 |</t>
+          <t>| BUG-17 | High | 02 | TC-COUPON-028 | 1 | [#18](https://github.com/DuyPham111/HW06/issues/18) |</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>| BUG-19 | Critical | 03 | TC-PRODUPD-101 *(chỉ verify-bugs.sh)* | 0 *(không chạy trong Newman — xem §3 BUG-19)* |</t>
+          <t>| BUG-18 | Critical | 02 | TC-COUPON-032, 039 | 2 | [#19](https://github.com/DuyPham111/HW06/issues/19) |</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>| BUG-20 | Critical | 03 | TC-PRODUPD-022, 038, 105 | 3 |</t>
+          <t>| BUG-19 | Critical | 03 | TC-PRODUPD-101 *(chỉ verify-bugs.sh)* | 0 *(không chạy trong Newman — xem §3 BUG-19)* | [#1](https://github.com/DuyPham111/HW06/issues/1) |</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>| BUG-21 | Critical | 03 | TC-PRODUPD-027, 028, 030, 102 | 4 |</t>
+          <t>| BUG-20 | Critical | 03 | TC-PRODUPD-022, 038, 105 | 3 | [#20](https://github.com/DuyPham111/HW06/issues/20) |</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>| BUG-22 | Critical | 03 | TC-PRODUPD-029 | 1 |</t>
+          <t>| BUG-21 | Critical | 03 | TC-PRODUPD-027, 028, 030, 102 | 4 | [#21](https://github.com/DuyPham111/HW06/issues/21) |</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>| BUG-23 | High | 03 | TC-PRODUPD-002, 004, 006, 007, 008, 009, 010 | 7 |</t>
+          <t>| BUG-22 | Critical | 03 | TC-PRODUPD-029 | 1 | [#22](https://github.com/DuyPham111/HW06/issues/22) |</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>| BUG-24 | Medium | 03 | TC-PRODUPD-015, 031 | 2 |</t>
+          <t>| BUG-23 | High | 03 | TC-PRODUPD-002, 004, 006, 007, 008, 009, 010 | 7 | [#23](https://github.com/DuyPham111/HW06/issues/23) |</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>| BUG-25 | Medium | 03 | TC-PRODUPD-014, 024, 025, 042, 043 | 5 |</t>
+          <t>| BUG-24 | Medium | 03 | TC-PRODUPD-015, 031 | 2 | [#24](https://github.com/DuyPham111/HW06/issues/24) |</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>| BUG-26 | Low | 03 | TC-PRODUPD-039 | 1 |</t>
+          <t>| BUG-25 | Medium | 03 | TC-PRODUPD-014, 024, 025, 042, 043 | 5 | [#25](https://github.com/DuyPham111/HW06/issues/25) |</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>| BUG-27 | High | 03 | TC-PRODUPD-045 | 1 |</t>
+          <t>| BUG-26 | Low | 03 | TC-PRODUPD-039 | 1 | [#26](https://github.com/DuyPham111/HW06/issues/26) |</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>| Tổng assertion đỏ map được | | | | 46 |</t>
+          <t>| BUG-27 | High | 03 | TC-PRODUPD-045 | 1 | [#27](https://github.com/DuyPham111/HW06/issues/27) |</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>| Tổng assertion đỏ map được | | | | 47 | |</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>&gt; 3 assertion đỏ chưa liệt kê ở trên (TC-COUPON-102/102c trung gian của chuỗi 5 bước, tính trùng</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>&gt; trong raw JSON do Newman đếm theo request chứ không theo bug; xem ghi chú trong</t>
+          <t>&gt; Khớp đúng 100% với tổng 47 đỏ ở test-cases/test-summary/summary.md — không còn assertion nào</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>&gt; test-cases/api-02-apply-coupon/audit.md) — không phải bug riêng, đã giải thích ở đó.</t>
+          <t>&gt; chưa giải thích được. *(Lượt chạy đầu 31/08/2026 từng có thêm 2 đỏ ở TC-COUPON-102/102c do dư</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>&gt; trạng thái môi trường, không phải bug — đã sửa bằng cách restart SUT sạch rồi chạy lại, xem</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>&gt; test-cases/api-02-apply-coupon/audit.md.)*</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10147,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>## 3. Chi tiết từng bug</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10157,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>### BUG-01 — Khóa tài khoản người khác (DoS) chỉ bằng email, không cần biết mật khẩu</t>
+          <t>## 3. Chi tiết từng bug</t>
         </is>
       </c>
     </row>
@@ -10177,66 +10167,66 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-01 — Khóa tài khoản người khác (DoS) chỉ bằng email, không cần biết mật khẩu</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>| API | API-01 · POST /api/login |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | Hệ quả bất lợi của FR-02 khi thiếu validate password tồn tại trước khi cộng bộ đếm sai |</t>
+          <t>| API | API-01 · POST /api/login |</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-031, TC-LOGIN-101, TC-LOGIN-101b |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js:32-66 — nhánh else (sai mật khẩu) không kiểm password !== undefined trước khi so sánh |</t>
+          <t>| Đặc tả bị vi phạm | Hệ quả bất lợi của FR-02 khi thiếu validate password tồn tại trước khi cộng bộ đếm sai |</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>| AI có bắt được không | Có (bước 4b), nhưng phải bổ sung 1 case SV (101b) mới đủ chứng minh hết chuỗi 3 request |</t>
+          <t>| Test case | TC-LOGIN-031, TC-LOGIN-101, TC-LOGIN-101b |</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>| Vị trí mã nguồn | server.js:32-66 — nhánh else (sai mật khẩu) không kiểm password !== undefined trước khi so sánh |</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Các bước tái hiện</t>
+          <t>| AI có bắt được không | Có (bước 4b), nhưng phải bổ sung 1 case SV (101b) mới đủ chứng minh hết chuỗi 3 request |</t>
         </is>
       </c>
     </row>
@@ -10246,103 +10236,103 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>`bash</t>
+          <t>Các bước tái hiện</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>bash bug-report/verify-bugs.sh 01</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>`bash</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>bash bug-report/verify-bugs.sh 01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kết quả thực tế (đã chạy qua Newman): 2 request POST /api/login chỉ có {email} (không có</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>password) tới cùng một tài khoản victim@x.com → cả 2 đều 401 (không lộ ngay), nhưng request thứ 3</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>— chủ nhân thật của tài khoản đăng nhập bằng đúng mật khẩu của mình — nhận **403 "Tài khoản đã</t>
+          <t>Kết quả thực tế (đã chạy qua Newman): 2 request POST /api/login chỉ có {email} (không có</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>bị khóa"**.</t>
+          <t>password) tới cùng một tài khoản victim@x.com → cả 2 đều 401 (không lộ ngay), nhưng request thứ 3</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>— chủ nhân thật của tài khoản đăng nhập bằng đúng mật khẩu của mình — nhận **403 "Tài khoản đã</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>bị khóa"**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>Kết quả mong đợi — request thiếu password phải bị từ chối ngay ở bước validate đầu vào</t>
         </is>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>(400), không được chạm tới nhánh cộng bộ đếm sai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ảnh hưởng — Bất kỳ ai biết một địa chỉ email đã đăng ký đều khóa được tài khoản đó trong 180</t>
+          <t>(400), không được chạm tới nhánh cộng bộ đếm sai.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>giây mà không cần biết một ký tự nào của mật khẩu — biến cơ chế chống brute-force (FR-02) thành</t>
-        </is>
-      </c>
+      <c r="A96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>công cụ tấn công từ chối dịch vụ nhắm vào người dùng cụ thể.</t>
+          <t>Ảnh hưởng — Bất kỳ ai biết một địa chỉ email đã đăng ký đều khóa được tài khoản đó trong 180</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>giây mà không cần biết một ký tự nào của mật khẩu — biến cơ chế chống brute-force (FR-02) thành</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>công cụ tấn công từ chối dịch vụ nhắm vào người dùng cụ thể.</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10342,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>### BUG-02 — Tài khoản bị khóa từ lần sai thứ 2, không phải "từ lần thứ 3" như FR-02</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -10362,124 +10352,124 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-02 — Tài khoản bị khóa từ lần sai thứ 2, không phải "từ lần thứ 3" như FR-02</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>| API | API-01 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-02: *"Nếu đăng nhập sai từ 3 lần trở lên liên tiếp, tài khoản bị tạm khóa"* |</t>
+          <t>| API | API-01 |</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-022 |</t>
+          <t>| Mức độ | High |</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js:54 — newAttempts = user.login_attempts + 2 (bước nhảy +2, không phải +1) |</t>
+          <t>| Đặc tả bị vi phạm | FR-02: *"Nếu đăng nhập sai từ 3 lần trở lên liên tiếp, tài khoản bị tạm khóa"* |</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>| Test case | TC-LOGIN-022 |</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kết quả thực tế: đăng nhập sai lần 1 → 401 (bộ đếm 0→2). Đăng nhập sai lần 2 → 401 (bộ đếm</t>
+          <t>| Vị trí mã nguồn | server.js:54 — newAttempts = user.login_attempts + 2 (bước nhảy +2, không phải +1) |</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2→4, đã ≥3, khóa được đặt ngầm ngay lúc này — nhưng response của chính request này chưa phản</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ánh). Request thứ 3 — dù là mật khẩu đúng — nhận 403, vì lúc kiểm đầu hàm, khóa đã tồn tại</t>
+          <t>Kết quả thực tế: đăng nhập sai lần 1 → 401 (bộ đếm 0→2). Đăng nhập sai lần 2 → 401 (bộ đếm</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>từ trước. Tổng cộng: khóa xảy ra sau 2 lần sai thật sự, không phải 3.</t>
+          <t>2→4, đã ≥3, khóa được đặt ngầm ngay lúc này — nhưng response của chính request này chưa phản</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ánh). Request thứ 3 — dù là mật khẩu đúng — nhận 403, vì lúc kiểm đầu hàm, khóa đã tồn tại</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>từ trước. Tổng cộng: khóa xảy ra sau 2 lần sai thật sự, không phải 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>Kết quả mong đợi — request thứ 3 với mật khẩu đúng phải thành công (200), vì FR-02 chỉ khóa khi</t>
         </is>
       </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>đã có 3 lần sai liên tiếp, và ở đây mới có 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>đã có 3 lần sai liên tiếp, và ở đây mới có 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>Ảnh hưởng — người dùng gõ nhầm mật khẩu 2 lần rồi nhớ ra và gõ đúng vẫn bị khóa oan 180 giây,</t>
         </is>
       </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>trải nghiệm tệ hơn đặc tả cam kết.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>trải nghiệm tệ hơn đặc tả cam kết.</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10479,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>### BUG-03 — Response đăng nhập thành công lộ nguyên mật khẩu dạng plaintext</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -10499,104 +10489,104 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-03 — Response đăng nhập thành công lộ nguyên mật khẩu dạng plaintext</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>| API | API-01 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | SEC-01: *"Mật khẩu không được lưu dưới dạng plaintext"* |</t>
+          <t>| API | API-01 |</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-028 |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js:32-50 — res.json({message, token, user}) với user là nguyên dòng DB |</t>
+          <t>| Đặc tả bị vi phạm | SEC-01: *"Mật khẩu không được lưu dưới dạng plaintext"* |</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>| Test case | TC-LOGIN-028 |</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kết quả thực tế:</t>
+          <t>| Vị trí mã nguồn | server.js:32-50 — res.json({message, token, user}) với user là nguyên dòng DB |</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>`json</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>{"message":"Login successful","token":"...","user":{"id":3,"name":"Dup1","email":"dup-test@x.com","password":"Abc12345!","role":"user","login_attempts":0,"locked_until":null,"reset_token":null,"shipping_address":null,"phone":null}}</t>
+          <t>Kết quả thực tế:</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>`json</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Trường password xuất hiện nguyên văn, đúng bằng giá trị vừa gửi lên, xác nhận nó cũng được</t>
+          <t>{"message":"Login successful","token":"...","user":{"id":3,"name":"Dup1","email":"dup-test@x.com","password":"Abc12345!","role":"user","login_attempts":0,"locked_until":null,"reset_token":null,"shipping_address":null,"phone":null}}</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>lưu plaintext trong DB (không hash) — vi phạm kép: vừa lưu sai, vừa trả về sai.</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Trường password xuất hiện nguyên văn, đúng bằng giá trị vừa gửi lên, xác nhận nó cũng được</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kết quả mong đợi — user trong response không được có field password.</t>
+          <t>lưu plaintext trong DB (không hash) — vi phạm kép: vừa lưu sai, vừa trả về sai.</t>
         </is>
       </c>
     </row>
@@ -10606,24 +10596,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>Kết quả mong đợi — user trong response không được có field password.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>Ảnh hưởng — ai chặn được response (log, proxy, trình duyệt debug) đều lấy được mật khẩu thật của</t>
         </is>
       </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>người dùng; kết hợp thói quen dùng lại mật khẩu, ảnh hưởng ra ngoài phạm vi hệ thống này.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>người dùng; kết hợp thói quen dùng lại mật khẩu, ảnh hưởng ra ngoài phạm vi hệ thống này.</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10623,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>### BUG-04 — Response lộ các cột nội bộ (login_attempts, locked_until, reset_token)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -10643,69 +10633,69 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-04 — Response lộ các cột nội bộ (login_attempts, locked_until, reset_token)</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>| API | API-01 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-029, TC-LOGIN-037 |</t>
+          <t>| API | API-01 |</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js:50 |</t>
+          <t>| Mức độ | High |</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>| Test case | TC-LOGIN-029, TC-LOGIN-037 |</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>| Vị trí mã nguồn | server.js:50 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
           <t>Cùng nguyên nhân với BUG-03 (trả nguyên dòng DB). Lộ reset_token nghiêm trọng hơn: nếu người dùng</t>
         </is>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>từng gọi quên mật khẩu, OTP còn hiệu lực bị lộ ngay trong response đăng nhập.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>từng gọi quên mật khẩu, OTP còn hiệu lực bị lộ ngay trong response đăng nhập.</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10705,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>### BUG-05 — JWT không có claim exp (không bao giờ hết hạn)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -10725,59 +10715,59 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-05 — JWT không có claim exp (không bao giờ hết hạn)</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>| API | API-01 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>| Mức độ | Medium |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | SEC-02: *"yêu cầu JWT Token hợp lệ"* |</t>
+          <t>| API | API-01 |</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-030 |</t>
+          <t>| Mức độ | Medium |</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js:50 — jwt.sign({id, role}, SECRET_KEY) không có option expiresIn |</t>
+          <t>| Đặc tả bị vi phạm | SEC-02: *"yêu cầu JWT Token hợp lệ"* |</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>| Test case | TC-LOGIN-030 |</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Token rò rỉ một lần thì có giá trị vĩnh viễn — không có cơ chế tự hết hạn để giới hạn thiệt hại.</t>
+          <t>| Vị trí mã nguồn | server.js:50 — jwt.sign({id, role}, SECRET_KEY) không có option expiresIn |</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10777,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Token rò rỉ một lần thì có giá trị vĩnh viễn — không có cơ chế tự hết hạn để giới hạn thiệt hại.</t>
         </is>
       </c>
     </row>
@@ -10797,7 +10787,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>### BUG-06 — Crash 500 + lộ stack trace khi thiếu đúng Content-Type: application/json</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -10807,121 +10797,121 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-06 — Crash 500 + lộ stack trace khi thiếu đúng Content-Type: application/json</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>| API | API-01 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-016 |</t>
+          <t>| API | API-01 |</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js:33 — const {email, password} = req.body khi req.body là undefined |</t>
+          <t>| Mức độ | High |</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>| Test case | TC-LOGIN-016 |</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Kết quả thực tế (curl, Content-Type: text/plain):</t>
+          <t>| Vị trí mã nguồn | server.js:33 — const {email, password} = req.body khi req.body là undefined |</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>`</t>
-        </is>
-      </c>
+      <c r="A186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TypeError: Cannot destructure property 'email' of 'req.body' as it is undefined.</t>
+          <t>Kết quả thực tế (curl, Content-Type: text/plain):</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>at D:\...\server.js:33:11</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>...9 dòng stack trace kèm đường dẫn tuyệt đối của server...</t>
+          <t>TypeError: Cannot destructure property 'email' of 'req.body' as it is undefined.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HTTP 500</t>
+          <t>at D:\...\server.js:33:11</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>...9 dòng stack trace kèm đường dẫn tuyệt đối của server...</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>HTTP 500</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
+          <t>`</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
           <t>Ảnh hưởng — lộ cấu trúc thư mục server, tên thư viện và phiên bản (body-parser, router) — dữ</t>
         </is>
       </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>liệu trinh sát hữu ích cho tấn công tiếp theo. Đây là lỗi 500 KHÔNG được catch, khác với BUG-07.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>liệu trinh sát hữu ích cho tấn công tiếp theo. Đây là lỗi 500 KHÔNG được catch, khác với BUG-07.</t>
         </is>
       </c>
     </row>
@@ -10931,7 +10921,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>### BUG-07 — HTML lỗi lộ stack trace khi body không phải JSON hợp lệ</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -10941,93 +10931,93 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-07 — HTML lỗi lộ stack trace khi body không phải JSON hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>| API | API-01 (và tương tự API-03, xem BUG-27) |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-036, TC-LOGIN-104 |</t>
+          <t>| API | API-01 (và tương tự API-03, xem BUG-27) |</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr"/>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>| Mức độ | High |</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Kết quả thực tế: gửi body không phải JSON (nhưng đúng Content-Type: application/json) →</t>
+          <t>| Test case | TC-LOGIN-036, TC-LOGIN-104 |</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>body-parser ném SyntaxError, Express dùng trang lỗi HTML mặc định, trả nguyên stack trace gồm</t>
-        </is>
-      </c>
+      <c r="A207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>đường dẫn tuyệt đối D:\Nam3\HK3\...\node_modules\body-parser\lib\types\json.js:109:10 và tên các</t>
+          <t>Kết quả thực tế: gửi body không phải JSON (nhưng đúng Content-Type: application/json) →</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>hàm nội bộ.</t>
+          <t>body-parser ném SyntaxError, Express dùng trang lỗi HTML mặc định, trả nguyên stack trace gồm</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>đường dẫn tuyệt đối D:\Nam3\HK3\...\node_modules\body-parser\lib\types\json.js:109:10 và tên các</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
+          <t>hàm nội bộ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
           <t>Ảnh hưởng — cùng loại rò rỉ thông tin với BUG-06, nhưng do một nguyên nhân khác (SUT chưa cấu</t>
         </is>
       </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>hình error-handling middleware tuỳ chỉnh để bắt lỗi parse và trả JSON gọn).</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>hình error-handling middleware tuỳ chỉnh để bắt lỗi parse và trả JSON gọn).</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11027,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>### BUG-08 — Đăng ký trùng email không bị chặn → tài khoản đăng ký sau mất quyền đăng nhập</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11047,135 +11037,135 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-08 — Đăng ký trùng email không bị chặn → tài khoản đăng ký sau mất quyền đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>| API | API-01 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-103 |</t>
+          <t>| API | API-01 |</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | database.js:47-56 — cột email TEXT không có UNIQUE |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>| Test case | TC-LOGIN-103 |</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Kết quả thực tế:</t>
+          <t>| Vị trí mã nguồn | database.js:47-56 — cột email TEXT không có UNIQUE |</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>`bash</t>
-        </is>
-      </c>
+      <c r="A226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>curl -X POST /api/register -d '{"email":"dup-test@x.com","password":"Abc12345!"}'  # id=3, thành công</t>
+          <t>Kết quả thực tế:</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>curl -X POST /api/register -d '{"email":"dup-test@x.com","password":"Zzz99999!"}'  # id=4, thành công</t>
+          <t>`bash</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>curl -X POST /api/login    -d '{"email":"dup-test@x.com","password":"Abc12345!"}'  # 200 (tài khoản id=3)</t>
+          <t>curl -X POST /api/register -d '{"email":"dup-test@x.com","password":"Abc12345!"}'  # id=3, thành công</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>curl -X POST /api/login    -d '{"email":"dup-test@x.com","password":"Zzz99999!"}'  # 401 !!!</t>
+          <t>curl -X POST /api/register -d '{"email":"dup-test@x.com","password":"Zzz99999!"}'  # id=4, thành công</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>curl -X POST /api/login    -d '{"email":"dup-test@x.com","password":"Abc12345!"}'  # 200 (tài khoản id=3)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE email=? luôn trả dòng đầu tiên khớp (id nhỏ nhất) — tài khoản đăng</t>
+          <t>curl -X POST /api/login    -d '{"email":"dup-test@x.com","password":"Zzz99999!"}'  # 401 !!!</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ký sau, dù đúng email và đúng mật khẩu của chính nó, không bao giờ đăng nhập được.</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE email=? luôn trả dòng đầu tiên khớp (id nhỏ nhất) — tài khoản đăng</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
+          <t>ký sau, dù đúng email và đúng mật khẩu của chính nó, không bao giờ đăng nhập được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
           <t>Ảnh hưởng — nếu 2 người vô tình dùng cùng email (hoặc 1 người đăng ký lại vì tưởng thất bại),</t>
         </is>
       </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>tài khoản mới tạo ra là vô dụng vĩnh viễn, không có thông báo lỗi nào cảnh báo trước.</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>tài khoản mới tạo ra là vô dụng vĩnh viễn, không có thông báo lỗi nào cảnh báo trước.</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11175,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>### BUG-09 — Account enumeration qua kênh phụ (so sánh 2 response)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11195,83 +11185,83 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-09 — Account enumeration qua kênh phụ (so sánh 2 response)</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>| API | API-01 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>| Mức độ | Medium |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-02: *"không để lộ chi tiết nguyên nhân"* |</t>
+          <t>| API | API-01 |</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>| Test case | TC-LOGIN-102 (đối chứng TC-LOGIN-023c) |</t>
+          <t>| Mức độ | Medium |</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr"/>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>| Đặc tả bị vi phạm | FR-02: *"không để lộ chi tiết nguyên nhân"* |</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Email không tồn tại: luôn 401 dù thử sai bao nhiêu lần. Email tồn tại: sau 2 lần sai, request</t>
+          <t>| Test case | TC-LOGIN-102 (đối chứng TC-LOGIN-023c) |</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>thứ 3 trả 403. Kẻ tấn công dò được chính xác email nào có tài khoản thật bằng cách gửi 3</t>
-        </is>
-      </c>
+      <c r="A250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>request sai liên tiếp và xem status code cuối — vi phạm đúng nguyên tắc FR-02 đã nêu, chỉ là qua kênh</t>
+          <t>Email không tồn tại: luôn 401 dù thử sai bao nhiêu lần. Email tồn tại: sau 2 lần sai, request</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>gián tiếp (nhiều request) thay vì lộ trong 1 response.</t>
+          <t>thứ 3 trả 403. Kẻ tấn công dò được chính xác email nào có tài khoản thật bằng cách gửi 3</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr"/>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>request sai liên tiếp và xem status code cuối — vi phạm đúng nguyên tắc FR-02 đã nêu, chỉ là qua kênh</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>gián tiếp (nhiều request) thay vì lộ trong 1 response.</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11271,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>### BUG-10 — Công thức phần trăm coupon sai dấu — giảm giá ÂM, tổng cuối LỚN HƠN đơn gốc</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11291,118 +11281,118 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-10 — Công thức phần trăm coupon sai dấu — giảm giá ÂM, tổng cuối LỚN HƠN đơn gốc</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>| API | API-02 · POST /api/apply-coupon |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-09: *"Loại percent: discount_amount = total × discount_value / 100"* |</t>
+          <t>| API | API-02 · POST /api/apply-coupon |</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-001, 042, 043 |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js — Math.floor(total_amount * (1 - coupon.discount_value)) (dùng 1 - value thay vì value / 100) |</t>
+          <t>| Đặc tả bị vi phạm | FR-09: *"Loại percent: discount_amount = total × discount_value / 100"* |</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr"/>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>| Test case | TC-COUPON-001, 042, 043 |</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Kết quả thực tế:</t>
+          <t>| Vị trí mã nguồn | server.js — Math.floor(total_amount * (1 - coupon.discount_value)) (dùng 1 - value thay vì value / 100) |</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>`bash</t>
-        </is>
-      </c>
+      <c r="A267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>curl -X POST /api/apply-coupon -d '{"code":"SAVE10","total_amount":500000}'</t>
+          <t>Kết quả thực tế:</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t># {"discount_amount":-4500000,"final_amount":5000000,"message":"Áp dụng thành công! Giảm 10%"}</t>
+          <t>`bash</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>curl -X POST /api/apply-coupon -d '{"code":"SAVE10","total_amount":500000}'</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Với discount_value = 10 (nghĩa là 10%), công thức tính 1 - 10 = -9, nhân với 500.000 ra</t>
+          <t># {"discount_amount":-4500000,"final_amount":5000000,"message":"Áp dụng thành công! Giảm 10%"}</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>-4.500.000 — một số âm khổng lồ. `final_amount = total - discount = 500.000 - (-4.500.000) =</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5.000.000` — gấp 10 lần giá gốc, được dán nhãn "Áp dụng thành công! Giảm 10%".</t>
+          <t>Với discount_value = 10 (nghĩa là 10%), công thức tính 1 - 10 = -9, nhân với 500.000 ra</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr"/>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>-4.500.000 — một số âm khổng lồ. `final_amount = total - discount = 500.000 - (-4.500.000) =</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Kết quả mong đợi — discount_amount = 500.000 × 10 / 100 = 50.000, final_amount = 450.000.</t>
+          <t>5.000.000` — gấp 10 lần giá gốc, được dán nhãn "Áp dụng thành công! Giảm 10%".</t>
         </is>
       </c>
     </row>
@@ -11412,31 +11402,31 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Ảnh hưởng — bug nghiêm trọng nhất về mặt tài chính trong cả 3 API: nếu số này được dùng để tính</t>
+          <t>Kết quả mong đợi — discount_amount = 500.000 × 10 / 100 = 50.000, final_amount = 450.000.</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>tiền thật ở bước checkout, khách hàng phải trả nhiều hơn giá gốc trong khi hệ thống báo "đã giảm</t>
-        </is>
-      </c>
+      <c r="A278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>giá thành công".</t>
+          <t>Ảnh hưởng — bug nghiêm trọng nhất về mặt tài chính trong cả 3 API: nếu số này được dùng để tính</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr"/>
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>tiền thật ở bước checkout, khách hàng phải trả nhiều hơn giá gốc trong khi hệ thống báo "đã giảm</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>giá thành công".</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11436,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>### BUG-11 — apply-coupon không yêu cầu xác thực dù FR-09 C4 đòi phải đăng nhập</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11456,76 +11446,76 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-11 — apply-coupon không yêu cầu xác thực dù FR-09 C4 đòi phải đăng nhập</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>| API | API-02 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-09 C4: *"Đã đăng nhập — Người dùng phải có JWT Token hợp lệ"* + SEC-02 |</t>
+          <t>| API | API-02 |</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-031 |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr"/>
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>| Đặc tả bị vi phạm | FR-09 C4: *"Đã đăng nhập — Người dùng phải có JWT Token hợp lệ"* + SEC-02 |</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Mọi request curl tới /api/apply-coupon trong suốt quá trình kiểm thử **đều thành công mà không</t>
+          <t>| Test case | TC-COUPON-031 |</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>gửi header Authorization** — xác nhận route hoàn toàn public, trái với điều kiện C4 đề bài định</t>
-        </is>
-      </c>
+      <c r="A293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>nghĩa.</t>
+          <t>Mọi request curl tới /api/apply-coupon trong suốt quá trình kiểm thử **đều thành công mà không</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr"/>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>gửi header Authorization** — xác nhận route hoàn toàn public, trái với điều kiện C4 đề bài định</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>nghĩa.</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11525,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>### BUG-12 — Biên min_order_amount dùng &gt; thay vì &gt;=</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11545,69 +11535,69 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-12 — Biên min_order_amount dùng &gt; thay vì &gt;=</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>| API | API-02 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-09 C3: *"Tổng đơn hàng &gt;= min_order_amount"* |</t>
+          <t>| API | API-02 |</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-004 |</t>
+          <t>| Mức độ | High |</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr"/>
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>| Đặc tả bị vi phạm | FR-09 C3: *"Tổng đơn hàng &gt;= min_order_amount"* |</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
+          <t>| Test case | TC-COUPON-004 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
           <t>total_amount đúng bằng min_order_amount (300.000) bị từ chối — theo đặc tả phải được chấp nhận.</t>
         </is>
       </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Đây cũng là case AI ban đầu chép sai theo hành vi code — xem audit.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Đây cũng là case AI ban đầu chép sai theo hành vi code — xem audit.md.</t>
         </is>
       </c>
     </row>
@@ -11617,7 +11607,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>### BUG-13 — IDOR qua user_id trong body: bỏ qua hoặc mượn hạn mức người khác</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11627,118 +11617,118 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-13 — IDOR qua user_id trong body: bỏ qua hoặc mượn hạn mức người khác</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>| API | API-02 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-09 C5 + SEC-02 (hệ quả của việc thiếu C4) |</t>
+          <t>| API | API-02 |</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-036, TC-COUPON-037 |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr"/>
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>| Đặc tả bị vi phạm | FR-09 C5 + SEC-02 (hệ quả của việc thiếu C4) |</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Kết quả thực tế:</t>
+          <t>| Test case | TC-COUPON-036, TC-COUPON-037 |</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>`bash</t>
-        </is>
-      </c>
+      <c r="A322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t># Da dung het 2/2 luot That (user_id that), nhung KHONG gui user_id:</t>
+          <t>Kết quả thực tế:</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>curl -X POST /api/apply-coupon -d '{"code":"VIP100","total_amount":400000}'</t>
+          <t>`bash</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t># -&gt; 200 thanh cong, BO QUA HOAN TOAN kiem tra han muc</t>
+          <t># Da dung het 2/2 luot That (user_id that), nhung KHONG gui user_id:</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>curl -X POST /api/apply-coupon -d '{"code":"VIP100","total_amount":400000}'</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Vì nhánh kiểm max_uses_per_user chỉ chạy if (user_id), client chỉ cần không gửi user_id để</t>
+          <t># -&gt; 200 thanh cong, BO QUA HOAN TOAN kiem tra han muc</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>áp dụng coupon giới hạn lượt vô hạn lần. Ngược lại, gửi user_id của người khác thì "mượn" được</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>hạn mức của họ (chưa dùng lần nào) trong khi vẫn đang dùng đúng token/trình duyệt của mình.</t>
+          <t>Vì nhánh kiểm max_uses_per_user chỉ chạy if (user_id), client chỉ cần không gửi user_id để</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr"/>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>áp dụng coupon giới hạn lượt vô hạn lần. Ngược lại, gửi user_id của người khác thì "mượn" được</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>hạn mức của họ (chưa dùng lần nào) trong khi vẫn đang dùng đúng token/trình duyệt của mình.</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11738,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>### BUG-14 — Checkout không xác thực total_amount phía server (price tampering)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11758,86 +11748,86 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-14 — Checkout không xác thực total_amount phía server (price tampering)</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>| API | API-02 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-034, TC-COUPON-101 |</t>
+          <t>| API | API-02 |</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js handler POST /api/checkout — INSERT INTO orders (..., total_amount, ...) dùng thẳng req.body.total_amount, không đọc lại giỏ hàng |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr"/>
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>| Test case | TC-COUPON-034, TC-COUPON-101 |</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
+          <t>| Vị trí mã nguồn | server.js handler POST /api/checkout — INSERT INTO orders (..., total_amount, ...) dùng thẳng req.body.total_amount, không đọc lại giỏ hàng |</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
           <t>Kết quả thực tế: giỏ hàng chứa iPhone 30.000.000đ, nhưng POST /api/checkout với</t>
         </is>
       </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>{"total_amount": 1} vẫn tạo đơn thành công với total_amount = 1 được lưu nguyên vào DB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
+          <t>{"total_amount": 1} vẫn tạo đơn thành công với total_amount = 1 được lưu nguyên vào DB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
           <t>Ảnh hưởng — kết hợp với BUG-21 (PUT sản phẩm không cần token), một kẻ tấn công có thể tự đặt giá</t>
         </is>
       </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>đơn hàng bất kỳ khi thanh toán, hoàn toàn không phụ thuộc giá thật của sản phẩm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>đơn hàng bất kỳ khi thanh toán, hoàn toàn không phụ thuộc giá thật của sản phẩm.</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11837,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>### BUG-15 — GET /api/orders/:id không yêu cầu xác thực (IDOR đọc đơn hàng)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11857,62 +11847,62 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-15 — GET /api/orders/:id không yêu cầu xác thực (IDOR đọc đơn hàng)</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>| API | API-02 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-033 |</t>
+          <t>| API | API-02 |</t>
         </is>
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr"/>
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>| Mức độ | High |</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
+          <t>| Test case | TC-COUPON-033 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
           <t>Đọc được chi tiết đơn hàng (địa chỉ giao hàng, tổng tiền, trạng thái) của bất kỳ ai chỉ bằng cách</t>
         </is>
       </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>đoán/duyệt id tuần tự, không cần token.</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>đoán/duyệt id tuần tự, không cần token.</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11912,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>### BUG-16 — Hủy được đơn đang shipping (vi phạm FR-10)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -11932,59 +11922,59 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-16 — Hủy được đơn đang shipping (vi phạm FR-10)</t>
         </is>
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>| API | API-02 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-10: *"chỉ được hủy khi pending hoặc confirmed"* |</t>
+          <t>| API | API-02 |</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-023 |</t>
+          <t>| Mức độ | High |</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js handler cancel — chỉ chặn status === "delivered" \|\| status === "canceled", thiếu chặn shipping |</t>
+          <t>| Đặc tả bị vi phạm | FR-10: *"chỉ được hủy khi pending hoặc confirmed"* |</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr"/>
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>| Test case | TC-COUPON-023 |</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| Vị trí mã nguồn | server.js handler cancel — chỉ chặn status === "delivered" \|\| status === "canceled", thiếu chặn shipping |</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11984,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>### BUG-17 — canceled không phải trạng thái kết thúc thật (chuyển được sang delivered)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12004,59 +11994,59 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-17 — canceled không phải trạng thái kết thúc thật (chuyển được sang delivered)</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>| API | API-02 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-10: *"delivered và canceled là trạng thái kết thúc — không được chuyển sang bất kỳ trạng thái nào khác"* |</t>
+          <t>| API | API-02 |</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-028 |</t>
+          <t>| Mức độ | High |</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | logic isValidTransition có riêng một nhánh if (currentStatus === "canceled" &amp;&amp; status === "delivered") isValidTransition = true — cố tình cho phép, không phải thiếu sót ngẫu nhiên |</t>
+          <t>| Đặc tả bị vi phạm | FR-10: *"delivered và canceled là trạng thái kết thúc — không được chuyển sang bất kỳ trạng thái nào khác"* |</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr"/>
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>| Test case | TC-COUPON-028 |</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| Vị trí mã nguồn | logic isValidTransition có riêng một nhánh if (currentStatus === "canceled" &amp;&amp; status === "delivered") isValidTransition = true — cố tình cho phép, không phải thiếu sót ngẫu nhiên |</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12056,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>### BUG-18 — Đổi trạng thái đơn không kiểm role admin (SEC-03)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12076,69 +12066,69 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-18 — Đổi trạng thái đơn không kiểm role admin (SEC-03)</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>| API | API-02 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | SEC-03: *"API Admin phải kiểm tra role = 'admin' trong Token, không chỉ kiểm tra sự tồn tại của Token"* |</t>
+          <t>| API | API-02 |</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>| Test case | TC-COUPON-032, TC-COUPON-039 |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr"/>
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>| Đặc tả bị vi phạm | SEC-03: *"API Admin phải kiểm tra role = 'admin' trong Token, không chỉ kiểm tra sự tồn tại của Token"* |</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
+          <t>| Test case | TC-COUPON-032, TC-COUPON-039 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
           <t>PUT /api/admin/orders/:id/status chỉ có authenticateToken (kiểm token hợp lệ), không kiểm</t>
         </is>
       </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>req.user.role === "admin" — user thường đổi được trạng thái đơn của bất kỳ ai.</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>req.user.role === "admin" — user thường đổi được trạng thái đơn của bất kỳ ai.</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12138,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>### BUG-19 — DoS: cập nhật thiếu trường rồi xem chi tiết làm SẬP TOÀN BỘ BACKEND</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12158,52 +12148,52 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-19 — DoS: cập nhật thiếu trường rồi xem chi tiết làm SẬP TOÀN BỘ BACKEND</t>
         </is>
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>| API | API-03 · PUT /api/products/:id + GET /api/products/:id |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical — nặng nhất trong cả bài |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-101 (chỉ trong verify-bugs.sh, không trong collection Postman — xem lý do ở docs/10-BUG-REPORT-GITHUB-ISSUES.md §6) |</t>
+          <t>| API | API-03 · PUT /api/products/:id + GET /api/products/:id |</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js:162 — if (row.id % 2 === 0) row.price = row.price.toString(); |</t>
+          <t>| Mức độ | Critical — nặng nhất trong cả bài |</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr"/>
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>| Test case | TC-PRODUPD-101 (chỉ trong verify-bugs.sh, không trong collection Postman — xem lý do ở docs/10-BUG-REPORT-GITHUB-ISSUES.md §6) |</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Các bước tái hiện</t>
+          <t>| Vị trí mã nguồn | server.js:162 — if (row.id % 2 === 0) row.price = row.price.toString(); |</t>
         </is>
       </c>
     </row>
@@ -12213,183 +12203,183 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>`bash</t>
+          <t>Các bước tái hiện</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>bash bug-report/verify-bugs.sh 19</t>
-        </is>
-      </c>
+      <c r="A413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>`bash</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr"/>
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>bash bug-report/verify-bugs.sh 19</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Kết quả thực tế — log thật từ terminal chạy node server.js:</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>`</t>
-        </is>
-      </c>
+      <c r="A417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>D:\...\eshop-sut\backend\server.js:162</t>
+          <t>Kết quả thực tế — log thật từ terminal chạy node server.js:</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>if (row.id % 2 === 0) row.price = row.price.toString();</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>^</t>
+          <t>D:\...\eshop-sut\backend\server.js:162</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>TypeError: Cannot read properties of null (reading 'toString')</t>
+          <t>if (row.id % 2 === 0) row.price = row.price.toString();</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>at Statement.&lt;anonymous&gt; (D:\...\server.js:162:49)</t>
+          <t>^</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>TypeError: Cannot read properties of null (reading 'toString')</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Node.js v22.16.0</t>
+          <t>at Statement.&lt;anonymous&gt; (D:\...\server.js:162:49)</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>`</t>
+          <t>...</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Toàn bộ tiến trình Node.js thoát hẳn — mọi request khác (kể cả của người dùng không liên quan)</t>
+          <t>Node.js v22.16.0</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>nhận ECONNREFUSED cho tới khi ai đó khởi động lại server thủ công.</t>
+          <t>`</t>
         </is>
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr"/>
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Toàn bộ tiến trình Node.js thoát hẳn — mọi request khác (kể cả của người dùng không liên quan)</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Nguyên nhân: PUT /api/products/:id với body thiếu price khiến câu lệnh UPDATE ghi NULL</t>
+          <t>nhận ECONNREFUSED cho tới khi ai đó khởi động lại server thủ công.</t>
         </is>
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>vào cột price (không validate, xem BUG-20). Với sản phẩm có id chẵn, lần GET kế tiếp gọi</t>
-        </is>
-      </c>
+      <c r="A430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>row.price.toString() trên null → ném lỗi không được bắt (uncaught) → crash tiến trình.</t>
+          <t>Nguyên nhân: PUT /api/products/:id với body thiếu price khiến câu lệnh UPDATE ghi NULL</t>
         </is>
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr"/>
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>vào cột price (không validate, xem BUG-20). Với sản phẩm có id chẵn, lần GET kế tiếp gọi</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
+          <t>row.price.toString() trên null → ném lỗi không được bắt (uncaught) → crash tiến trình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
           <t>Kết quả mong đợi — PUT thiếu trường phải bị từ chối (400) trước khi chạm DB; và dù có xảy ra</t>
         </is>
       </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>dữ liệu NULL, GET không được để một lỗi kiểu dữ liệu làm sập cả tiến trình.</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Ảnh hưởng — DoS toàn hệ thống chỉ với 2 request tuần tự, không cần quyền admin thật (route</t>
+          <t>dữ liệu NULL, GET không được để một lỗi kiểu dữ liệu làm sập cả tiến trình.</t>
         </is>
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>này cũng không yêu cầu xác thực — xem BUG-21). Đây là bug bị phát hiện ngoài ý muốn trong lúc dò</t>
-        </is>
-      </c>
+      <c r="A437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>lỗi khác — xem ghi chú đầy đủ ở test-cases/api-03-product-update/audit.md.</t>
+          <t>Ảnh hưởng — DoS toàn hệ thống chỉ với 2 request tuần tự, không cần quyền admin thật (route</t>
         </is>
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr"/>
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>này cũng không yêu cầu xác thực — xem BUG-21). Đây là bug bị phát hiện ngoài ý muốn trong lúc dò</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>lỗi khác — xem ghi chú đầy đủ ở test-cases/api-03-product-update/audit.md.</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12389,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>### BUG-20 — Cập nhật một phần xoá mất dữ liệu (set NULL) thay vì giữ nguyên</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12409,107 +12399,107 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-20 — Cập nhật một phần xoá mất dữ liệu (set NULL) thay vì giữ nguyên</t>
         </is>
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>| API | API-03 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | FR-15: *"Khi Sửa một sản phẩm, chỉ sản phẩm đó bị thay đổi — các sản phẩm khác giữ nguyên"* (ngụ ý ở cấp trường: trường không gửi phải giữ nguyên) |</t>
+          <t>| API | API-03 |</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-022, 038, 105 |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js handler PUT — UPDATE products SET name=?, price=?, ... WHERE id=? luôn ghi đè cả 5 cột bằng giá trị từ body, kể cả khi field không được gửi (undefined → NULL) |</t>
+          <t>| Đặc tả bị vi phạm | FR-15: *"Khi Sửa một sản phẩm, chỉ sản phẩm đó bị thay đổi — các sản phẩm khác giữ nguyên"* (ngụ ý ở cấp trường: trường không gửi phải giữ nguyên) |</t>
         </is>
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr"/>
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>| Test case | TC-PRODUPD-022, 038, 105 |</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Kết quả thực tế: PUT /api/products/3 chỉ gửi {"name": "..."} → price, description,</t>
+          <t>| Vị trí mã nguồn | server.js handler PUT — UPDATE products SET name=?, price=?, ... WHERE id=? luôn ghi đè cả 5 cột bằng giá trị từ body, kể cả khi field không được gửi (undefined → NULL) |</t>
         </is>
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>imageUrl, category_id của sản phẩm đều thành NULL. PUT với body rỗng {} xoá sạch cả 5</t>
-        </is>
-      </c>
+      <c r="A453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>trường cùng lúc.</t>
+          <t>Kết quả thực tế: PUT /api/products/3 chỉ gửi {"name": "..."} → price, description,</t>
         </is>
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr"/>
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>imageUrl, category_id của sản phẩm đều thành NULL. PUT với body rỗng {} xoá sạch cả 5</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Ảnh hưởng — bất kỳ form sửa sản phẩm nào chỉ gửi các trường người dùng thực sự chỉnh (hành vi</t>
+          <t>trường cùng lúc.</t>
         </is>
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>thông thường của UI) đều vô tình xoá sạch dữ liệu các trường còn lại — và trên sản phẩm id chẵn,</t>
-        </is>
-      </c>
+      <c r="A457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>còn trực tiếp gây ra BUG-19.</t>
+          <t>Ảnh hưởng — bất kỳ form sửa sản phẩm nào chỉ gửi các trường người dùng thực sự chỉnh (hành vi</t>
         </is>
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr"/>
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>thông thường của UI) đều vô tình xoá sạch dữ liệu các trường còn lại — và trên sản phẩm id chẵn,</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>còn trực tiếp gây ra BUG-19.</t>
         </is>
       </c>
     </row>
@@ -12519,7 +12509,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>### BUG-21 — PUT/DELETE /api/products/:id không yêu cầu xác thực</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12529,83 +12519,83 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-21 — PUT/DELETE /api/products/:id không yêu cầu xác thực</t>
         </is>
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>| API | API-03 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>| Đặc tả bị vi phạm | SEC-02 + FR-15: *"Admin có thể Thêm/Sửa/Xóa sản phẩm"* |</t>
+          <t>| API | API-03 |</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-027, 028, 030, 102 |</t>
+          <t>| Mức độ | Critical |</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>| Đối chứng | TC-PRODUPD-035 (PUT /api/categories/:id — route "anh em" cùng nhóm admin — CÓ authenticateToken, xác nhận đây là thiếu sót không nhất quán, không phải chủ đích) |</t>
+          <t>| Đặc tả bị vi phạm | SEC-02 + FR-15: *"Admin có thể Thêm/Sửa/Xóa sản phẩm"* |</t>
         </is>
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr"/>
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>| Test case | TC-PRODUPD-027, 028, 030, 102 |</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>PUT và DELETE trên sản phẩm thành công với **không có header, token rác, hay bất kỳ trạng thái</t>
+          <t>| Đối chứng | TC-PRODUPD-035 (PUT /api/categories/:id — route "anh em" cùng nhóm admin — CÓ authenticateToken, xác nhận đây là thiếu sót không nhất quán, không phải chủ đích) |</t>
         </is>
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>xác thực nào** — route hoàn toàn không có middleware authenticateToken, khác hẳn route</t>
-        </is>
-      </c>
+      <c r="A473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>/api/categories/:id cùng nhóm chức năng.</t>
+          <t>PUT và DELETE trên sản phẩm thành công với **không có header, token rác, hay bất kỳ trạng thái</t>
         </is>
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr"/>
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>xác thực nào** — route hoàn toàn không có middleware authenticateToken, khác hẳn route</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>/api/categories/:id cùng nhóm chức năng.</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12605,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>### BUG-22 — PUT /api/products/:id không kiểm role admin (SEC-03)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12625,62 +12615,62 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-22 — PUT /api/products/:id không kiểm role admin (SEC-03)</t>
         </is>
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>| API | API-03 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>| Mức độ | Critical |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-029 |</t>
+          <t>| API | API-03 |</t>
         </is>
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr"/>
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>| Mức độ | Critical |</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
+          <t>| Test case | TC-PRODUPD-029 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
           <t>(Về lý thuyết đây là lớp bảo vệ thứ 2 sau BUG-21; vì BUG-21 đã bỏ hẳn xác thực nên lớp role-check</t>
         </is>
       </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>càng không tồn tại — ghi riêng vì đây là 2 lớp phòng thủ độc lập theo đúng SEC-02/SEC-03.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>càng không tồn tại — ghi riêng vì đây là 2 lớp phòng thủ độc lập theo đúng SEC-02/SEC-03.)</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12680,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>### BUG-23 — Không validate name/price/category_id theo FR-15</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12700,69 +12690,69 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-23 — Không validate name/price/category_id theo FR-15</t>
         </is>
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>| API | API-03 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-002, 004, 006, 007, 008, 009, 010 |</t>
+          <t>| API | API-03 |</t>
         </is>
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr"/>
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>| Mức độ | High |</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Tổng hợp 7 test case: name rỗng, name 256 ký tự (vượt 255), price = 0, price âm, price sai</t>
+          <t>| Test case | TC-PRODUPD-002, 004, 006, 007, 008, 009, 010 |</t>
         </is>
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>kiểu (chuỗi chữ), category_id không tồn tại, category_id thiếu — tất cả đều được chấp nhận</t>
-        </is>
-      </c>
+      <c r="A500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>(200), không một ràng buộc nào trong FR-15 được thực thi ở phía server.</t>
+          <t>Tổng hợp 7 test case: name rỗng, name 256 ký tự (vượt 255), price = 0, price âm, price sai</t>
         </is>
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr"/>
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>kiểu (chuỗi chữ), category_id không tồn tại, category_id thiếu — tất cả đều được chấp nhận</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>(200), không một ràng buộc nào trong FR-15 được thực thi ở phía server.</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12762,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>### BUG-24 — :id sai định dạng/không hợp lệ vẫn xử lý như thành công</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12782,69 +12772,69 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-24 — :id sai định dạng/không hợp lệ vẫn xử lý như thành công</t>
         </is>
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>| API | API-03 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>| Mức độ | Medium |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-015, TC-PRODUPD-031 |</t>
+          <t>| API | API-03 |</t>
         </is>
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr"/>
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>| Mức độ | Medium |</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>:id = "abc" hoặc chứa payload SQLi-shape (1 OR 1=1) đều nhận 200 "Product updated" thay vì</t>
+          <t>| Test case | TC-PRODUPD-015, TC-PRODUPD-031 |</t>
         </is>
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>400 — vì parameterized query chỉ đơn giản không khớp dòng nào (this.changes = 0), nhưng handler</t>
-        </is>
-      </c>
+      <c r="A514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>không kiểm giá trị này trước khi trả về thành công.</t>
+          <t>:id = "abc" hoặc chứa payload SQLi-shape (1 OR 1=1) đều nhận 200 "Product updated" thay vì</t>
         </is>
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr"/>
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>400 — vì parameterized query chỉ đơn giản không khớp dòng nào (this.changes = 0), nhưng handler</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>không kiểm giá trị này trước khi trả về thành công.</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12844,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>### BUG-25 — :id không tồn tại vẫn báo thành công/trả 200 {} thay vì 404</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12864,62 +12854,62 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-25 — :id không tồn tại vẫn báo thành công/trả 200 {} thay vì 404</t>
         </is>
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>| API | API-03 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>| Mức độ | Medium |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-014, 024, 025, 042, 043 |</t>
+          <t>| API | API-03 |</t>
         </is>
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr"/>
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>| Mức độ | Medium |</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
+          <t>| Test case | TC-PRODUPD-014, 024, 025, 042, 043 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
           <t>PUT/GET trên sản phẩm không tồn tại (kể cả sau khi DELETE) đều không trả 404 — GET trả</t>
         </is>
       </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>200 {}, PUT trả 200 {"message":"Product updated"} dù không có dòng nào bị ảnh hưởng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>200 {}, PUT trả 200 {"message":"Product updated"} dù không có dòng nào bị ảnh hưởng.</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12919,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>### BUG-26 — price bị ép kiểu thành string khi id chẵn</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -12939,76 +12929,76 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-26 — price bị ép kiểu thành string khi id chẵn</t>
         </is>
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>| API | API-03 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>| Mức độ | Low |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-039 |</t>
+          <t>| API | API-03 |</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>| Vị trí mã nguồn | server.js:162 |</t>
+          <t>| Mức độ | Low |</t>
         </is>
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr"/>
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>| Test case | TC-PRODUPD-039 |</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Độc lập với BUG-19/20 (crash khi giá trị là null): ngay cả khi price là số hợp lệ, GET sản</t>
+          <t>| Vị trí mã nguồn | server.js:162 |</t>
         </is>
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>phẩm id chẵn luôn trả price dạng chuỗi ("100000"), trong khi id lẻ trả number</t>
-        </is>
-      </c>
+      <c r="A542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>(100000) — client phải tự xử lý 2 kiểu dữ liệu khác nhau cho cùng một field.</t>
+          <t>Độc lập với BUG-19/20 (crash khi giá trị là null): ngay cả khi price là số hợp lệ, GET sản</t>
         </is>
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr"/>
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>phẩm id chẵn luôn trả price dạng chuỗi ("100000"), trong khi id lẻ trả number</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>(100000) — client phải tự xử lý 2 kiểu dữ liệu khác nhau cho cùng một field.</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13008,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>### BUG-27 — HTML lỗi lộ stack trace khi body PUT không phải JSON hợp lệ</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -13028,62 +13018,62 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>| | |</t>
+          <t>### BUG-27 — HTML lỗi lộ stack trace khi body PUT không phải JSON hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>| API | API-03 |</t>
+          <t>| | |</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>| Mức độ | High |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>| Test case | TC-PRODUPD-045 |</t>
+          <t>| API | API-03 |</t>
         </is>
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="inlineStr"/>
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>| Mức độ | High |</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
+          <t>| Test case | TC-PRODUPD-045 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
           <t>Cùng nguyên nhân và mức độ với BUG-07 (API-01) — body-parser ném lỗi parse, Express trả trang HTML</t>
         </is>
       </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>mặc định kèm đường dẫn tuyệt đối của server.</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>mặc định kèm đường dẫn tuyệt đối của server.</t>
         </is>
       </c>
     </row>
@@ -13093,7 +13083,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>## 4. Giả thuyết đã bị loại sau khi kiểm chứng</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -13103,52 +13093,52 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>| # | Giả thuyết | Đã kiểm bằng gì | Vì sao bị loại |</t>
+          <t>## 4. Giả thuyết đã bị loại sau khi kiểm chứng</t>
         </is>
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>| 1 | *(API-02)* "Có thể nhảy cóc pending → shipping hoặc pending → delivered" | curl PUT admin/orders/status trực tiếp | Cả hai đều bị chặn đúng — code có kiểm đủ điều kiện transition hợp lệ cho các nhánh này, chỉ riêng canceled → delivered là lỗ hổng thật (BUG-17) |</t>
+          <t>| # | Giả thuyết | Đã kiểm bằng gì | Vì sao bị loại |</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>| 2 | *(API-02)* "user thường huỷ được đơn của người khác qua PUT /orders/:id/cancel" | curl với admin_token gọi huỷ đơn của user | 404, không phải lỗ hổng — endpoint này CÓ lọc đúng WHERE user_id = req.user.id, admin gọi vào đơn người khác thì không tìm thấy. Giữ lại làm case đối chứng ở TC-COUPON-105 |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>| 3 | *(API-02)* "VIP100 cho phép dùng vượt quá 2 lượt/người khi dùng đúng user_id" | Chuỗi 5 request thật (TC-COUPON-102→102e) | Sai — khi user_id đúng và thật, giới hạn 2 lượt hoạt động chính xác (400 ở lượt thứ 3). Lỗ hổng thật nằm ở việc user_id do CLIENT tự khai (BUG-13), không phải ở logic đếm |</t>
+          <t>| 1 | *(API-02)* "Có thể nhảy cóc pending → shipping hoặc pending → delivered" | curl PUT admin/orders/status trực tiếp | Cả hai đều bị chặn đúng — code có kiểm đủ điều kiện transition hợp lệ cho các nhánh này, chỉ riêng canceled → delivered là lỗ hổng thật (BUG-17) |</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>| 4 | *(API-01)* "SQL injection qua email bypass được đăng nhập" | 3 dạng payload SQLi khác nhau qua curl | Không bypass được — db.get(..., [email], ...) dùng tham số hoá đúng chuẩn (SEC-05 đạt cho endpoint này) |</t>
+          <t>| 2 | *(API-02)* "user thường huỷ được đơn của người khác qua PUT /orders/:id/cancel" | curl với admin_token gọi huỷ đơn của user | 404, không phải lỗ hổng — endpoint này CÓ lọc đúng WHERE user_id = req.user.id, admin gọi vào đơn người khác thì không tìm thấy. Giữ lại làm case đối chứng ở TC-COUPON-105 |</t>
         </is>
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr"/>
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>| 3 | *(API-02)* "VIP100 cho phép dùng vượt quá 2 lượt/người khi dùng đúng user_id" | Chuỗi 5 request thật (TC-COUPON-102→102e) | Sai — khi user_id đúng và thật, giới hạn 2 lượt hoạt động chính xác (400 ở lượt thứ 3). Lỗ hổng thật nằm ở việc user_id do CLIENT tự khai (BUG-13), không phải ở logic đếm |</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>## 5. Rủi ro / câu hỏi nghiệp vụ (chưa đủ căn cứ gọi là bug)</t>
+          <t>| 4 | *(API-01)* "SQL injection qua email bypass được đăng nhập" | 3 dạng payload SQLi khác nhau qua curl | Không bypass được — db.get(..., [email], ...) dùng tham số hoá đúng chuẩn (SEC-05 đạt cho endpoint này) |</t>
         </is>
       </c>
     </row>
@@ -13158,26 +13148,36 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>| # | Quan sát | Vì sao chưa gọi là bug |</t>
+          <t>## 5. Rủi ro / câu hỏi nghiệp vụ (chưa đủ căn cứ gọi là bug)</t>
         </is>
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>| R-01 | POST /api/coupon-usage không tự động được gọi bởi POST /api/checkout — phải gọi tay | Có thể là thiết kế cố ý (tách bước ghi nhận usage khỏi checkout để FE tự quyết định khi nào coi là "đã dùng"); cần hỏi lại yêu cầu nghiệp vụ thật trước khi kết luận là thiếu sót |</t>
+          <t>| # | Quan sát | Vì sao chưa gọi là bug |</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>| R-01 | POST /api/coupon-usage không tự động được gọi bởi POST /api/checkout — phải gọi tay | Có thể là thiết kế cố ý (tách bước ghi nhận usage khỏi checkout để FE tự quyết định khi nào coi là "đã dùng"); cần hỏi lại yêu cầu nghiệp vụ thật trước khi kết luận là thiếu sót |</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t>| R-02 | imageUrl chấp nhận bất kỳ chuỗi nào, kể cả javascript: | Đặc tả không định nghĩa validate URL; rủi ro thật chỉ phát sinh nếu frontend render trực tiếp giá trị này mà không escape (thuộc phạm vi SEC-04 ở tầng UI, ngoài phạm vi 3 API đã chọn của bài này) |</t>
         </is>

--- a/excel/23127183_HW06_TestCases.xlsx
+++ b/excel/23127183_HW06_TestCases.xlsx
@@ -464,7 +464,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>&gt; Sinh luc: 2026-09-02T15:27:57.633Z</t>
+          <t>&gt; Sinh luc: 2026-09-02T17:12:00.823Z</t>
         </is>
       </c>
     </row>
@@ -488,21 +488,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>| api-01-login | 53 | 53 | 44 | 9 | 23127183_api-01-login_20260902-222409.json |</t>
+          <t>| api-01-login | 53 | 53 | 44 | 9 | 23127183_api-01-login_20260903-001136.json |</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>| api-02-apply-coupon | 59 | 59 | 46 | 13 | 23127183_api-02-apply-coupon_20260902-222617.json |</t>
+          <t>| api-02-apply-coupon | 59 | 59 | 46 | 13 | 23127183_api-02-apply-coupon_20260903-001136.json |</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>| api-03-product-update | 51 | 51 | 26 | 25 | 23127183_api-03-product-update_20260902-222733.json |</t>
+          <t>| api-03-product-update | 51 | 51 | 26 | 25 | 23127183_api-03-product-update_20260903-001136.json |</t>
         </is>
       </c>
     </row>
